--- a/output/2026-10-03_18_Malesia_Perlis_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-03_18_Malesia_Perlis_Utensilerie_e_Macchine_Utensili.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda reale dal 1986 (Reg. n. 199101009246/219559-X), sede a Kangar + filiale a Sungai Petani (Kedah). Hardware store e fornitore industriale B2B: dealer ufficiale Bosch (elettroutensili), distributore autorizzato Linde Malaysia (gas industriali), fasteners, pompe, attrezzature saldatura, DPI. Confermato su sito ufficiale. WhatsApp: 016-422 5570.</t>
+          <t>Azienda reale dal 1986 (Reg. n. 199101009246/219559-X), sede a Kangar + filiale a Sungai Petani (Kedah). Hardware store e fornitore industriale B2B: dealer ufficiale Bosch (elettroutensili), distributore autorizzato Linde Malaysia (gas industriali), fasteners, pompe, attrezzature saldatura, DPI. Confermato su sito ufficiale. WhatsApp: 016-422 5570. [DUPLICATO — vedi anche: 2026-10-01_05_Malesia_Kedah_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,7 +516,6 @@
           <t>ProTool Works</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Arau, Perlis</t>
@@ -532,7 +531,6 @@
           <t>019-546 9064</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Esistenza confermata su directory business (Cybo), indirizzo e telefono coerenti; tool store in zona commerciale di Arau. Profilo B2B non pienamente verificabile per assenza di sito ufficiale.</t>
@@ -540,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -550,7 +548,6 @@
           <t>KDT Maju Enterprise</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Arau, Perlis</t>
@@ -561,8 +558,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Fornitore B2B di attrezzature industriali, generatori e materiale per saldatura, attivo in Arau (fonte: directory business). Esiste una sede omonima in Tepi Highway/Jalan Kampung Tengah risultata 'permanently closed', trattata come entita distinta e scartata.</t>
